--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
   <si>
     <t>Filename</t>
   </si>
@@ -808,682 +808,679 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8959,0.0020,0.0506,0.0114</t>
-  </si>
-  <si>
-    <t>0.0053,0.0005,0.0002,0.9982</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.4010,0.0000,0.0000,0.9075</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9849,0.0004,0.0051,0.0032</t>
+  </si>
+  <si>
+    <t>0.0143,0.0001,0.0007,0.9957</t>
+  </si>
+  <si>
+    <t>0.9958,0.0001,0.0001,0.0025</t>
+  </si>
+  <si>
+    <t>0.0634,0.0002,0.0000,0.9784</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0016,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0006,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0017,0.9977,0.0004</t>
+  </si>
+  <si>
+    <t>0.8188,0.0020,0.1830,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9980,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9693,0.0001,0.0341,0.0002</t>
+  </si>
+  <si>
+    <t>0.0483,0.0059,0.9285,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0028,0.9899,0.0007</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9482,0.0422,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.7370,0.0037,0.1478,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0103,0.9688,0.0170,0.0001</t>
+  </si>
+  <si>
+    <t>0.9698,0.0013,0.0182,0.0013</t>
+  </si>
+  <si>
+    <t>0.9866,0.0005,0.0066,0.0001</t>
+  </si>
+  <si>
+    <t>0.2048,0.8245,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9956,0.0126,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0256,0.9909,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.0007,0.9922,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0184,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0015,0.9939,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.0225,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.1077,0.0000,0.9873</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1276,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0228,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0014,0.9907,0.0019</t>
+  </si>
+  <si>
+    <t>0.9977,0.0025,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0029,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0045,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9728,0.9866,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.2062,0.9951,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9831,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9994,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0001,0.0069,0.0000</t>
+  </si>
+  <si>
+    <t>0.9397,0.0021,0.0617,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9966,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.8802,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9581,0.9909,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.0036,0.9973</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0011,0.0004,0.9983</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0006,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0009,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9950,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9763,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9909,0.7455,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9818,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0085,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.9677,0.0009,0.0195,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0287,0.9637,0.0113,0.0007</t>
+  </si>
+  <si>
+    <t>0.8933,0.0113,0.0516,0.0007</t>
+  </si>
+  <si>
+    <t>0.8463,0.0008,0.1744,0.0002</t>
+  </si>
+  <si>
+    <t>0.8359,0.0561,0.0251,0.0010</t>
+  </si>
+  <si>
+    <t>0.6717,0.0014,0.2993,0.0012</t>
+  </si>
+  <si>
+    <t>0.0057,0.0053,0.0067,0.9897</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9921,0.9367,0.0000</t>
+  </si>
+  <si>
+    <t>0.8907,0.1359,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.1257,0.9003,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0488,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8335,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0720,0.9943,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0076,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0002,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9419,0.0036,0.0447,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.9465,0.0077,0.0204,0.0010</t>
+  </si>
+  <si>
+    <t>0.1070,0.0000,0.0001,0.9680</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0235,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9693,0.0000</t>
+  </si>
+  <si>
+    <t>0.0164,0.9717,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.1271,0.9105,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0538,0.0000,0.0000,0.9963</t>
+  </si>
+  <si>
+    <t>0.0001,0.0118,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.6535,0.2628,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0854,0.9210,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9934,0.0017,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9484,0.0121,0.0207,0.0013</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0041,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0085,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.1547,0.0008,0.8879,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0023,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9489,0.0006,0.0581,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0094,0.9903,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9694,0.0005,0.0291,0.0002</t>
-  </si>
-  <si>
-    <t>0.0191,0.0092,0.9446,0.0040</t>
-  </si>
-  <si>
-    <t>0.0310,0.0014,0.9725,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0097,0.0001,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.8377,0.1604,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.2262,0.0010,0.7703,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.9978,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9358,0.0016,0.0349,0.0013</t>
-  </si>
-  <si>
-    <t>0.9662,0.0016,0.0153,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.9912,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9615,0.1684,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.0056,0.9789,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.0241,0.9977,0.0004</t>
-  </si>
-  <si>
-    <t>0.0085,0.0004,0.9889,0.0009</t>
-  </si>
-  <si>
-    <t>0.0032,0.0196,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.7877,0.0000,0.9204</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0095,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0047,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3250,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.0005,0.9943,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0004,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0004,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9658,0.0443,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8571,0.1732,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5881,0.4930,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.3318,0.0039,0.7491,0.0004</t>
+  </si>
+  <si>
+    <t>0.8881,0.1679,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9361,0.0492,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9876,0.0044,0.0044,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9994,0.0004</t>
+  </si>
+  <si>
+    <t>0.0529,0.0121,0.8669,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.0141,0.9846,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0009,0.9945,0.0011</t>
+  </si>
+  <si>
+    <t>0.1718,0.3633,0.1441,0.0037</t>
+  </si>
+  <si>
+    <t>0.0363,0.8807,0.0318,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0017,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.3683,0.0015,0.6387,0.0012</t>
+  </si>
+  <si>
+    <t>0.0549,0.0444,0.8515,0.0031</t>
+  </si>
+  <si>
+    <t>0.0020,0.9970,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0315,0.9797,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0201,0.9841,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.6991,0.3230,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0605,0.9556,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8068,0.0452,0.0073,0.0106</t>
+  </si>
+  <si>
+    <t>0.1410,0.0083,0.8078,0.0026</t>
+  </si>
+  <si>
+    <t>0.9637,0.0014,0.0306,0.0005</t>
+  </si>
+  <si>
+    <t>0.0044,0.0004,0.9959,0.0010</t>
+  </si>
+  <si>
+    <t>0.0070,0.0042,0.9872,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0952,0.9880,0.0003</t>
+  </si>
+  <si>
+    <t>0.6587,0.0046,0.2986,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.2204,0.9584,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0021,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9505,0.0568,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0022,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0032,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9997,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.5069,0.8308,0.0011</t>
+  </si>
+  <si>
+    <t>0.0347,0.0022,0.9787,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0037,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0004,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0047,0.9961,0.0024</t>
+  </si>
+  <si>
+    <t>0.9855,0.0013,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0000,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9930,0.0066,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0005,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9865,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0031,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0003,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9561,0.0135,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.2024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.0001,0.0133,0.9933</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0016,0.0006,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0005,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9868,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9816,0.9761,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.5000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9686,0.9898,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9834,0.9517,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9977,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0002,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9971,0.0070,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4981,0.5769,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0953,0.0354,0.8145,0.0063</t>
-  </si>
-  <si>
-    <t>0.0537,0.0005,0.9644,0.0001</t>
-  </si>
-  <si>
-    <t>0.4873,0.2313,0.0369,0.0008</t>
-  </si>
-  <si>
-    <t>0.8520,0.0161,0.0477,0.0011</t>
-  </si>
-  <si>
-    <t>0.0018,0.0316,0.0008,0.9937</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9851,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.9596,0.0347,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9440,0.0730,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9839,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0424,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0105,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0041,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9503,0.0018,0.0449,0.0018</t>
-  </si>
-  <si>
-    <t>0.0464,0.0008,0.9683,0.0002</t>
-  </si>
-  <si>
-    <t>0.6506,0.0101,0.2698,0.0013</t>
-  </si>
-  <si>
-    <t>0.2157,0.0000,0.0000,0.9452</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9768,0.9856,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9966,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1453,0.9001,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.5238,0.0000,0.0000,0.9222</t>
-  </si>
-  <si>
-    <t>0.0004,0.0066,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0002,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.0311,0.9660,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6924,0.2870,0.0034,0.0008</t>
-  </si>
-  <si>
-    <t>0.9561,0.0259,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.9812,0.0066,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8962,0.1377,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7517,0.3042,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.8061,0.2849,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.1249,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.4121,0.6524,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0010,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9915,0.0056,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9683,0.0039,0.0243,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0049,0.9955,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0215,0.0058,0.9572,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0024,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.2643,0.0102,0.6766,0.0023</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.2241,0.0133,0.6989,0.0070</t>
-  </si>
-  <si>
-    <t>0.2137,0.0067,0.7635,0.0003</t>
-  </si>
-  <si>
-    <t>0.0160,0.9816,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9475,0.0009,0.0589,0.0001</t>
-  </si>
-  <si>
-    <t>0.8032,0.0013,0.1732,0.0055</t>
-  </si>
-  <si>
-    <t>0.0180,0.3692,0.5956,0.0026</t>
-  </si>
-  <si>
-    <t>0.0448,0.9646,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9984,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1460,0.8896,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.1157,0.9084,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0146,0.9872,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.7404,0.1934,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0004,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9820,0.0040,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.0251,0.0943,0.8067,0.0088</t>
-  </si>
-  <si>
-    <t>0.9431,0.0051,0.0345,0.0010</t>
-  </si>
-  <si>
-    <t>0.0039,0.0019,0.9946,0.0024</t>
-  </si>
-  <si>
-    <t>0.0033,0.0693,0.9491,0.0003</t>
-  </si>
-  <si>
-    <t>0.0348,0.0041,0.9664,0.0001</t>
-  </si>
-  <si>
-    <t>0.7183,0.0025,0.2266,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0183,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0033,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0031,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0099,0.2149,0.8325,0.0015</t>
-  </si>
-  <si>
-    <t>0.7142,0.0007,0.3137,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0108,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0043,0.9957,0.0007</t>
-  </si>
-  <si>
-    <t>0.9342,0.0028,0.0557,0.0002</t>
-  </si>
-  <si>
-    <t>0.8617,0.0003,0.2283,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0024,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0090,0.0308,0.9486,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0059,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.0055,0.9902,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0299,0.0017,0.9681,0.0015</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9960,0.0017</t>
-  </si>
-  <si>
-    <t>0.0034,0.0167,0.9577,0.0011</t>
-  </si>
-  <si>
-    <t>0.3907,0.0000,0.0024,0.7809</t>
-  </si>
-  <si>
-    <t>0.0030,0.0136,0.0001,0.9978</t>
-  </si>
-  <si>
-    <t>0.0116,0.0001,0.0015,0.9960</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.7629,0.0010,0.0003,0.2882</t>
+    <t>0.9996,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0045,0.0033,0.9897,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.1742,0.9504,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0072,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0869,0.0017,0.8521,0.0275</t>
+  </si>
+  <si>
+    <t>0.0063,0.0019,0.9869,0.0034</t>
+  </si>
+  <si>
+    <t>0.0050,0.0031,0.9852,0.0026</t>
+  </si>
+  <si>
+    <t>0.9446,0.0000,0.0012,0.0868</t>
+  </si>
+  <si>
+    <t>0.0003,0.0489,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.8422,0.0009,0.0000,0.1320</t>
   </si>
 </sst>
 </file>
@@ -2023,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2286,7 +2283,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
         <v>293</v>
@@ -2384,7 +2381,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>300</v>
@@ -2482,7 +2479,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>307</v>
@@ -2527,7 +2524,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2541,7 +2538,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2555,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2569,7 +2566,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2583,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2597,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2611,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2625,7 +2622,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2639,7 +2636,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2653,7 +2650,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2667,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2681,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2695,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2709,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2723,7 +2720,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2737,7 +2734,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2751,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2765,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2779,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2793,7 +2790,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2807,7 +2804,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2821,7 +2818,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2835,7 +2832,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2849,7 +2846,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2863,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2877,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,7 +2888,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,10 +2899,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2919,7 +2916,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2933,7 +2930,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2947,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2961,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2975,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2989,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,10 +2997,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3017,7 +3014,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,10 +3025,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,7 +3042,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3059,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3073,7 +3070,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3101,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3115,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3129,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3199,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3213,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3227,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3269,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3283,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3297,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3311,7 +3308,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3325,7 +3322,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3339,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3353,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3367,7 +3364,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3381,7 +3378,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3462,7 +3459,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
         <v>367</v>
@@ -3476,7 +3473,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>368</v>
@@ -3549,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3563,7 +3560,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>310</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3577,7 +3574,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3605,7 +3602,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,10 +3613,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3633,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3647,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3661,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3675,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3689,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3703,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>272</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3717,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3731,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,10 +3739,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,10 +3753,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3773,7 +3770,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3787,7 +3784,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3801,7 +3798,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3815,7 +3812,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3829,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3857,7 +3854,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3871,7 +3868,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3885,7 +3882,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3899,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3913,7 +3910,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3941,7 +3938,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3955,7 +3952,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,7 +3966,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3983,7 +3980,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3997,7 +3994,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4025,7 +4022,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4039,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4053,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,10 +4061,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4081,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4095,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4106,10 +4103,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4123,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4137,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4151,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4193,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4207,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4235,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4249,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>272</v>
+        <v>378</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4316,7 +4313,7 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
         <v>417</v>
@@ -4333,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4347,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4375,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4389,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4403,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4417,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4431,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4445,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4459,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4473,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4487,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4501,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4515,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,10 +4537,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4557,7 +4554,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,10 +4565,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,10 +4579,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4599,7 +4596,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4613,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4627,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4641,7 +4638,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4652,10 +4649,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4669,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4697,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4711,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4725,7 +4722,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4739,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4753,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4767,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4781,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4795,7 +4792,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4809,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4823,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4837,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4851,7 +4848,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4865,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4879,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4893,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4907,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4946,7 +4943,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
         <v>460</v>
@@ -4960,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
         <v>461</v>
@@ -4977,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4991,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,7 +5002,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5019,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5033,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5047,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5061,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5075,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5089,7 +5086,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,7 +5100,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5117,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5131,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5145,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5159,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5173,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5187,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>408</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5201,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5215,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5229,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>271</v>
+        <v>476</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5299,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>291</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5313,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5327,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5341,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,10 +5349,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5369,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5383,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5397,7 +5394,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5411,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5425,7 +5422,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
